--- a/Stats Sheet/Round Gaps/Scarlett.xlsx
+++ b/Stats Sheet/Round Gaps/Scarlett.xlsx
@@ -55,7 +55,7 @@
     <x:t>lolitsbrian</x:t>
   </x:si>
   <x:si>
-    <x:t>LqndSlide</x:t>
+    <x:t>lqndslide</x:t>
   </x:si>
   <x:si>
     <x:t>MinecrafNinja</x:t>
